--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HCX33\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78CD4F6E-C32A-450E-88C0-25B02036FAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5ABDCB-6080-7F4D-B214-C3F54E886F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -147,6 +147,38 @@
   </si>
   <si>
     <t xml:space="preserve">https://github.com/LeoHou1013 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inverse-Transform Method</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bootstrap Estimate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generate random variables using inverse CDFs and compare simulated results with theoretical properties</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exponential Distribution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Convolution Methods</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulate the sum of independent exponential random variables and compare the simulated distribution with the theoretical gamma distribution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -463,17 +495,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -481,12 +513,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -494,67 +526,94 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -572,7 +631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -592,7 +651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
@@ -612,7 +671,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
@@ -632,7 +691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
@@ -652,27 +711,27 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>21</v>
       </c>

--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5ABDCB-6080-7F4D-B214-C3F54E886F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5DC293-FB16-4940-A731-BA9B5F58BB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -158,10 +158,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Generate random variables using inverse CDFs and compare simulated results with theoretical properties</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Exponential Distribution</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -170,15 +166,19 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Simulate the sum of independent exponential random variables and compare the simulated distribution with the theoretical gamma distribution</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>N/A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulate the sum of independent exponential random variables and compare the simulated distribution with the theoretical gamma distribution.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generate random variables using inverse CDFs and compare simulated results with theoretical properties.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -569,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5DC293-FB16-4940-A731-BA9B5F58BB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A115FB8F-672A-6D4D-B04E-598E227F79F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="1000" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -170,15 +170,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Simulate the sum of independent exponential random variables and compare the simulated distribution with the theoretical gamma distribution.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Generate random variables using inverse CDFs and compare simulated results with theoretical properties.</t>
+    <t>Generating random variables using the CDF and comparing our simulated results with the true density by the mean, variance, and histograms.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median and visualizing datasets using histograms.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A115FB8F-672A-6D4D-B04E-598E227F79F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A16E15-0477-FB48-BFCF-E67F9C52F18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="1000" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -166,10 +166,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>N/A</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Simulate the sum of independent exponential random variables and compare the simulated distribution with the theoretical gamma distribution.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -179,6 +175,10 @@
   </si>
   <si>
     <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median and visualizing datasets using histograms.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>healthcare</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -547,7 +547,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -577,7 +577,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A16E15-0477-FB48-BFCF-E67F9C52F18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6F8C73-FC01-E347-80D6-3F22F9FF2194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="1000" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="740" windowWidth="29040" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -174,11 +174,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Use bootstrap resampling to estimate the sampling distributions of the mean and median and visualizing datasets using histograms.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>healthcare</t>
+    <t>healthcare data</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use bootstrap resampling on a healthcare dataset to estimate the sampling distributions of the mean and median, and visualizing datasets using histograms.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blesswmy/Desktop/STA380/STA380project/Submissions/GroupFormation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC6F8C73-FC01-E347-80D6-3F22F9FF2194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8005766F-EE01-CF4A-9F06-6B714F325469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="740" windowWidth="29040" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="740" windowWidth="29040" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -174,11 +174,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>healthcare data</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Use bootstrap resampling on a healthcare dataset to estimate the sampling distributions of the mean and median, and visualizing datasets using histograms.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healthcare Data</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +599,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
